--- a/sdwan_devices.xlsx
+++ b/sdwan_devices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,16 +441,6 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>device-type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>system-ip</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>reachability</t>
         </is>
       </c>
@@ -458,52 +448,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dc-cedge01</t>
+          <t>vmanage</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.10.1.11</t>
+          <t>10.10.1.1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>vedge</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>10.10.1.11</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>unreachable</t>
+          <t>reachable</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>my-10-f33116-mc01</t>
+          <t>vsmart</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.10.1.13</t>
+          <t>10.10.1.5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t>vedge</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>10.10.1.13</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>reachable</t>
         </is>
@@ -512,25 +482,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>site2-cedge01</t>
+          <t>vbond</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.10.1.15</t>
+          <t>10.10.1.3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t>vedge</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>10.10.1.15</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>reachable</t>
         </is>
@@ -539,52 +499,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>site3-vedge01</t>
+          <t>dc-cedge01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.10.1.17</t>
+          <t>10.10.1.11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>vedge</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>10.10.1.17</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>reachable</t>
+          <t>unreachable</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vbond</t>
+          <t>my-10-f33116-mc01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.10.1.3</t>
+          <t>10.10.1.13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
-        <is>
-          <t>vbond</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>10.10.1.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>reachable</t>
         </is>
@@ -593,25 +533,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vmanage</t>
+          <t>site2-cedge01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10.10.1.1</t>
+          <t>10.10.1.15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>vmanage</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>10.10.1.1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>reachable</t>
         </is>
@@ -620,25 +550,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vsmart</t>
+          <t>site3-vedge01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.10.1.5</t>
+          <t>10.10.1.17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>vsmart</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>10.10.1.5</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>reachable</t>
         </is>
